--- a/daily_matches/job_matches_2026-03-26.xlsx
+++ b/daily_matches/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gameplay Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>SciPlay</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, CI/CD, Snowflake, Redshift, Hadoop, PostgreSQL, MySQL, Tableau</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Redshift, BigQuery, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ec3c629adbbaf3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=95ded9f2441e8d33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Venatore</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Databricks, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff27edbece16f3be</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a327f492c5e4e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Git, Snowflake, Redshift, MySQL, NoSQL, Tableau, Python</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,392 +601,112 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc8f82f83aa02d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (AI/ML) | MS/PhD - Summer 2026</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, PyTorch, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e4b4a4a40b46f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Senior Industrial IT/OT Integration Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Jenkins, Git, Snowflake, Databricks, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a919c767d24ca70c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e758666dafbe3df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consulting &amp; Architecture</t>
+          <t>Applied AI ML, Senior Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20db9f4dc99c51dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Science Infrastructure</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=505f486ab10cd0e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Science Infrastructure</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92293490ab806248</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Science Infrastructure</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4418e8c02ccc7420</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Science Infrastructure</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fceb677420fc9b64</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Science Infrastructure</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fa8141c0554e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Science Infrastructure</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15461bdaeba9ba74</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Transformation Engineer (Mon-Fri 8:00am-4:30pm)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>RK Logistics Group</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Chandler, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75d194b89150b336</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer , Backend</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Aircall</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, Kubernetes, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97fa2133e7e8f42d</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b7fd5371f7dd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-26.xlsx
+++ b/daily_matches/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gameplay Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SciPlay</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Redshift, BigQuery, Git, Snowflake, BigQuery</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ec3c629adbbaf3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ba7ebaed0abacc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ded9f2441e8d33</t>
+          <t>https://www.indeed.com/viewjob?jk=29df1a8ac15025cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Grata</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
+          <t>RAG, Glue, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a327f492c5e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>S3, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6ee3b702a37e1c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,77 +636,217 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Industrial IT/OT Integration Specialist</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, Cortex, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e758666dafbe3df</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied AI ML, Senior Associate</t>
+          <t>Senior Software Development Engineer, IT MFG &amp; TPG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=838dd5a6e658b0f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Data Foundation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca3c0444e26e4a13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Data Foundation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98f5ee2b9206fc96</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Builder Supply Link</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b7fd5371f7dd</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18971bb97c69bf5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer / Architect — AI JSON/MongoDB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, PostgreSQL, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d00c05822944cec7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-26.xlsx
+++ b/daily_matches/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Indev</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, Redshift, Git, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ba7ebaed0abacc</t>
+          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - CRS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>AGILYSYS, INC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Generative AI, LangChain, Copilot, Prompt Engineering, TensorFlow, PyTorch, Data Lake, Git, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29df1a8ac15025cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c352671e8dbbe5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grata</t>
+          <t>Novelis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Apache Airflow, Snowflake, BigQuery, Redshift, PostgreSQL, MySQL</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e149cd4b58c9f54f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, RAG, Data Lake, Kafka, Hadoop, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,252 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b6ee3b702a37e1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dbt Engineer II or III</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Blue Cross of Idaho</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Meridian, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Snowflake Engineer II or III</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Blue Cross of Idaho</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Meridian, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Cortex, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer, IT MFG &amp; TPG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=838dd5a6e658b0f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Data Foundation</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3c0444e26e4a13</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Data Foundation</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98f5ee2b9206fc96</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Builder Supply Link</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>S3, CI/CD, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18971bb97c69bf5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer / Architect — AI JSON/MongoDB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, PostgreSQL, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d00c05822944cec7</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-26.xlsx
+++ b/daily_matches/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GEN AI Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Indev</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, EC2, Redshift, Git, Redshift, Kafka, Hadoop</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, PyTorch, AWS SageMaker, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f22c3539a16cf2c7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - CRS</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AGILYSYS, INC.</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Copilot, Prompt Engineering, TensorFlow, PyTorch, Data Lake, Git, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Snowflake, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c352671e8dbbe5</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Novelis</t>
+          <t>Schellman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e149cd4b58c9f54f</t>
+          <t>https://www.indeed.com/viewjob?jk=5aca29f6bc54e326</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kafka, Hadoop, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, Terraform, Snowflake, BigQuery, PostgreSQL, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,952 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior, Data Scientist - Gen AI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>San Bruno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, Git, NoSQL, Tableau, Matplotlib, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e3105a10657d137</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Founding Backend Engineer – AI &amp; Data</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Clipbook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, CI/CD, BigQuery, Kafka, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff010956a5d58f78</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a110160500019794</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c77e778c130f5327</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd1bccdd0a77033d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bef5813910ca2a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=421a77688915c0be</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e785c0ad2588ae40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8f79e76f742f5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8641dcf2903290b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f62dc777b832c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bdd708bd8f3e0be</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4d78a7e7f6f7a59</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=873af033aa4e5628</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d740d03605ca1917</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f1b0372229f9671</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b507af92279c1cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2318080604427e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be4f880075cbaa7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f6b5b7b2d3a362d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer - Cloud</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Guidewire</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25848b3ed9a71cd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>National Interstate</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98696f421b2321b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Builder Supply Link</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=530480aed242f686</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chabez Tech</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=977b6cb24c8ac2aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Expressable</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CERO Developer L1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PyTorch, FastAPI, Docker, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f8887fd5c1263cd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-26.xlsx
+++ b/daily_matches/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GEN AI Solution Architect</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, PyTorch, AWS SageMaker, FastAPI</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22c3539a16cf2c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, MLflow, CI/CD, Snowflake, BigQuery, Kafka</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Schellman</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aca29f6bc54e326</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Research &amp; Agentic Engineer Hybrid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, Terraform, Snowflake, BigQuery, PostgreSQL, NoSQL, Tableau</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f4807c43ca136</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist - Gen AI</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Bruno, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, Git, NoSQL, Tableau, Matplotlib, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Git, Snowflake, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e3105a10657d137</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Founding Backend Engineer – AI &amp; Data</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clipbook</t>
+          <t>Open Access Technology International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, BigQuery, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=96412c233010f923</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff010956a5d58f78</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a110160500019794</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Computer Systems Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Qb Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, S3, Snowflake, Kafka, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77e778c130f5327</t>
+          <t>https://www.indeed.com/viewjob?jk=4093ba79aee80b70</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Data Scientist, Data Insights</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1bccdd0a77033d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ef11ff7c0131ea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Software Engineer, AI Developer Tools</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bef5813910ca2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8324fc50ef37ad25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Mobile Software Engineer Hybrid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Git, BigQuery, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=421a77688915c0be</t>
+          <t>https://www.indeed.com/viewjob?jk=b4223c09f9357c6e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>VASS Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Generative AI, RAG, S3, FastAPI, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e785c0ad2588ae40</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Software Engineer, Gift Registry</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, BigQuery, Docker, Git, BigQuery, PostgreSQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8f79e76f742f5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4434083778fa8d3c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>United Stones, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8641dcf2903290b</t>
+          <t>https://www.indeed.com/viewjob?jk=43031ffaf4953d93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f62dc777b832c05</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c96c2d5b9d775e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>National Interstate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richfield, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd708bd8f3e0be</t>
+          <t>https://www.indeed.com/viewjob?jk=1b547cc37ab01554</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d78a7e7f6f7a59</t>
+          <t>https://www.indeed.com/viewjob?jk=eef2f6461545be31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>MACHINE LEARNING ENGINEER INTERN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, XGBoost, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=873af033aa4e5628</t>
+          <t>https://www.indeed.com/viewjob?jk=e554d3ed87980105</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Associate Data Scientist (GIS Specialist)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d740d03605ca1917</t>
+          <t>https://www.indeed.com/viewjob?jk=3076bd71bea72fbe</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Applied AI Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f1b0372229f9671</t>
+          <t>https://www.indeed.com/viewjob?jk=16977e50ff99ea1d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Applied AI Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b507af92279c1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2df0f3c110d8b4e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Applied AI Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2318080604427e4</t>
+          <t>https://www.indeed.com/viewjob?jk=587cbba7ad0c07e4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Applied AI Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,252 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4f880075cbaa7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Databricks, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6b5b7b2d3a362d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Software Engineer - Cloud</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Guidewire</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25848b3ed9a71cd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>National Interstate</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Richfield, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98696f421b2321b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Builder Supply Link</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>S3, CI/CD, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=530480aed242f686</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Chabez Tech</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=977b6cb24c8ac2aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Expressable</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CERO Developer L1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, PyTorch, FastAPI, Docker, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8887fd5c1263cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c59bc1195338dc65</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-26.xlsx
+++ b/daily_matches/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Ronin Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, GCP Vertex AI, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=00d9114936398c43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>AI Engineer, Generative AI, RAG, BigQuery, Dataflow, CI/CD, Jenkins, Git, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>TensorFlow, PyTorch, S3, Glue, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Research &amp; Agentic Engineer Hybrid</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, Redshift, Docker, Kubernetes, Snowflake, Databricks, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f4807c43ca136</t>
+          <t>https://www.indeed.com/viewjob?jk=a92d3aa09f2f357e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Git, Snowflake, Tableau, Power BI</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, PySpark, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer - AI Coding Agents</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Open Access Technology International</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96412c233010f923</t>
+          <t>https://www.indeed.com/viewjob?jk=35bcbbec1272ccc4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>Generative AI, BigQuery, Dataflow, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Kafka, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Computer Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qb Energy</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, S3, Snowflake, Kafka, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Data Lake, Kubernetes, Apache Airflow, Terraform, Git, Databricks, Hadoop, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4093ba79aee80b70</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Data Insights</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ef11ff7c0131ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e6f6e4a464ec7c64</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Developer Tools</t>
+          <t>Software AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8324fc50ef37ad25</t>
+          <t>https://www.indeed.com/viewjob?jk=1192ba756f092cc3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mobile Software Engineer Hybrid</t>
+          <t>Senior Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HackerOne</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Git, BigQuery, R</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, GCP Vertex AI, Azure ML, Git, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4223c09f9357c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac74beef94b63a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VASS Inc</t>
+          <t>HackerOne</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, FastAPI, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, GCP Vertex AI, Azure ML, Git, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
+          <t>https://www.indeed.com/viewjob?jk=97f8b20df394f7f7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Gift Registry</t>
+          <t>Senior Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>HackerOne</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Git, BigQuery, PostgreSQL, MongoDB, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, GCP Vertex AI, Azure ML, Git, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4434083778fa8d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5e473f922322055</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Senior Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Stones, Inc</t>
+          <t>HackerOne</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, GCP Vertex AI, Azure ML, Git, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43031ffaf4953d93</t>
+          <t>https://www.indeed.com/viewjob?jk=e8065799f7c12f40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c96c2d5b9d775e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb908bc50200e1c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>National Interstate</t>
+          <t>HackerOne</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, GCP Vertex AI, Azure ML, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b547cc37ab01554</t>
+          <t>https://www.indeed.com/viewjob?jk=d25dc0860271cd9a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HackerOne</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, GCP Vertex AI, Azure ML, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef2f6461545be31</t>
+          <t>https://www.indeed.com/viewjob?jk=f255fd3ab75084f3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING ENGINEER INTERN</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>Renters Warehouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, XGBoost, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e554d3ed87980105</t>
+          <t>https://www.indeed.com/viewjob?jk=1b62399358dd44ee</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Data Scientist (GIS Specialist)</t>
+          <t>Senior Salesforce Administrator - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Python, SQL, R, Bayesian</t>
+          <t>Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3076bd71bea72fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=a1e3d1cfa1338f0b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied AI Scientist</t>
+          <t>AI - Center of Excellence Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Nabors Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16977e50ff99ea1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b69d6973e8eb57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applied AI Scientist</t>
+          <t>AI Advisor, Software Development Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, Power BI, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2df0f3c110d8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8670782e12a5aca1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Applied AI Scientist</t>
+          <t>DevOps - Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>August Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,217 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587cbba7ad0c07e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a8f1865e2258af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Applied AI Scientist</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Technical Data Analyst</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VSP Vision</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Git, Snowflake, Redshift, Tableau, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fcb9b1f9fae6de2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Coding Agents</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NiCE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c59bc1195338dc65</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1c486234dac06b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lowell, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f139ce0c50f5248</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist / Advanced Analytics Specialist</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c01e61ca8a8ee790</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Technology I</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mettawa, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c71b5e116385edb7</t>
         </is>
       </c>
     </row>
